--- a/data/trans_dic/P25A$molestias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,27; 23,31</t>
+          <t>9,79; 24,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 18,45</t>
+          <t>4,89; 19,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 14,92</t>
+          <t>3,68; 15,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,26</t>
+          <t>0,0; 15,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 27,96</t>
+          <t>7,38; 28,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,69; 26,49</t>
+          <t>7,57; 26,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 20,06</t>
+          <t>8,01; 20,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 18,75</t>
+          <t>7,08; 18,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,68; 16,55</t>
+          <t>6,44; 17,23</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 30,1</t>
+          <t>11,45; 28,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 17,2</t>
+          <t>2,53; 16,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,71; 14,89</t>
+          <t>2,72; 15,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 34,49</t>
+          <t>10,03; 33,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 20,63</t>
+          <t>3,53; 20,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 22,87</t>
+          <t>5,83; 23,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,61; 28,39</t>
+          <t>13,37; 27,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 15,13</t>
+          <t>4,25; 14,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,24</t>
+          <t>5,45; 15,73</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23,41; 40,0</t>
+          <t>21,78; 40,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 18,23</t>
+          <t>7,91; 18,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 24,98</t>
+          <t>9,47; 24,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 37,42</t>
+          <t>4,64; 37,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,8</t>
+          <t>0,0; 34,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,24; 37,23</t>
+          <t>20,25; 36,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 15,24</t>
+          <t>6,53; 14,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 22,87</t>
+          <t>9,34; 22,86</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,41; 22,4</t>
+          <t>13,26; 22,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 15,0</t>
+          <t>8,04; 15,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 24,65</t>
+          <t>14,29; 24,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 28,05</t>
+          <t>9,33; 27,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 16,22</t>
+          <t>3,45; 15,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,36</t>
+          <t>1,21; 10,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,75; 21,43</t>
+          <t>13,69; 21,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 13,28</t>
+          <t>7,33; 13,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 18,91</t>
+          <t>11,01; 19,28</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 17,67</t>
+          <t>3,95; 18,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,67; 16,12</t>
+          <t>5,66; 16,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 28,79</t>
+          <t>13,68; 28,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 33,27</t>
+          <t>8,67; 36,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,64</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95; 35,29</t>
+          <t>15,56; 36,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 20,23</t>
+          <t>7,08; 20,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 12,71</t>
+          <t>4,48; 12,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 29,32</t>
+          <t>16,63; 28,33</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,66</t>
+          <t>0,0; 78,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 17,95</t>
+          <t>1,98; 18,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,95; 27,83</t>
+          <t>8,08; 30,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,28; 33,35</t>
+          <t>6,38; 34,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,24</t>
+          <t>1,79; 16,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 26,12</t>
+          <t>7,47; 26,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,77; 32,68</t>
+          <t>7,71; 31,33</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,78; 21,93</t>
+          <t>15,77; 22,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 13,2</t>
+          <t>8,56; 12,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,12; 19,28</t>
+          <t>12,97; 19,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,4; 19,27</t>
+          <t>10,33; 18,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 12,25</t>
+          <t>6,13; 12,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 17,7</t>
+          <t>10,32; 17,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,33</t>
+          <t>15,34; 20,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,94</t>
+          <t>8,38; 11,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,74; 17,34</t>
+          <t>12,91; 17,51</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco</t>
+          <t>Población cuyo motivo para dejar de fumar fue, al menos, las molestias por causa del tabaco (tasa de respuesta: 91,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8890; 22352</t>
+          <t>9386; 23799</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5436; 20680</t>
+          <t>5484; 22073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3233; 13929</t>
+          <t>3432; 14760</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 6571</t>
+          <t>0; 5859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3263; 14456</t>
+          <t>3818; 14856</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4723; 16263</t>
+          <t>4650; 16014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11155; 26872</t>
+          <t>10729; 26842</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12281; 30708</t>
+          <t>11587; 30217</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10339; 25610</t>
+          <t>9960; 26665</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9239; 24031</t>
+          <t>9142; 22969</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2285; 15463</t>
+          <t>2273; 15056</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1978; 10849</t>
+          <t>1982; 11430</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3944; 13956</t>
+          <t>4057; 13555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1922; 11153</t>
+          <t>1908; 11142</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3348; 15305</t>
+          <t>3903; 15594</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16371; 34159</t>
+          <t>16084; 32946</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5523; 21781</t>
+          <t>6123; 21165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8131; 22696</t>
+          <t>7619; 21993</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24982; 42686</t>
+          <t>23245; 42834</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13255; 29536</t>
+          <t>12818; 30370</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9076; 24548</t>
+          <t>9311; 24159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1138; 9122</t>
+          <t>1131; 9238</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2033</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4721</t>
+          <t>0; 4509</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27838; 48807</t>
+          <t>26548; 47331</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13037; 30051</t>
+          <t>12868; 29262</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9987; 25494</t>
+          <t>10409; 25478</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36489; 60957</t>
+          <t>36072; 61020</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24931; 47836</t>
+          <t>25650; 48506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32537; 56128</t>
+          <t>32543; 56731</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5952; 17766</t>
+          <t>5907; 17438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4106; 18349</t>
+          <t>3901; 17316</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>960; 8978</t>
+          <t>1051; 9348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46122; 71903</t>
+          <t>45909; 72881</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31402; 57393</t>
+          <t>31690; 59194</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33920; 59455</t>
+          <t>34619; 60627</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1953; 11236</t>
+          <t>2512; 11460</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7215; 20494</t>
+          <t>7192; 21079</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15051; 31007</t>
+          <t>14730; 31154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2924; 11811</t>
+          <t>3078; 13061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 8082</t>
+          <t>0; 6968</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10496; 24769</t>
+          <t>10923; 25441</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7181; 20043</t>
+          <t>7014; 20187</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8841; 24991</t>
+          <t>8797; 24097</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29837; 52164</t>
+          <t>29581; 50401</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1460</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1589</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4381</t>
+          <t>0; 4354</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>972; 8794</t>
+          <t>969; 8965</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4844; 16957</t>
+          <t>4922; 18337</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2270; 12051</t>
+          <t>2304; 12505</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>964; 8855</t>
+          <t>977; 9031</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4133; 17489</t>
+          <t>4999; 17510</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3239; 13631</t>
+          <t>3215; 13067</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98389; 136750</t>
+          <t>98376; 137248</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69519; 107720</t>
+          <t>69852; 104258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79415; 116761</t>
+          <t>78537; 115709</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26066; 48311</t>
+          <t>25904; 47492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23830; 47113</t>
+          <t>23570; 49017</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33156; 59206</t>
+          <t>34525; 60067</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>130992; 177721</t>
+          <t>134096; 177437</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>99105; 143303</t>
+          <t>100550; 143881</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>119717; 162963</t>
+          <t>121357; 164615</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25A$molestias-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P25A$molestias-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 24,82</t>
+          <t>9,89; 25,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,89; 19,7</t>
+          <t>4,92; 19,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,68; 15,81</t>
+          <t>3,34; 15,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,39</t>
+          <t>0,0; 16,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 28,74</t>
+          <t>7,73; 27,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 26,08</t>
+          <t>6,59; 26,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 20,04</t>
+          <t>7,78; 19,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 18,45</t>
+          <t>7,19; 18,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 17,23</t>
+          <t>6,48; 16,47</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 28,77</t>
+          <t>12,31; 29,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 16,74</t>
+          <t>2,6; 15,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 15,69</t>
+          <t>2,85; 15,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 33,5</t>
+          <t>9,57; 34,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 20,61</t>
+          <t>3,67; 20,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 23,3</t>
+          <t>5,36; 23,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,37; 27,39</t>
+          <t>13,71; 27,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,25; 14,7</t>
+          <t>4,26; 15,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,73</t>
+          <t>5,6; 15,82</t>
         </is>
       </c>
     </row>
@@ -898,22 +898,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,78; 40,14</t>
+          <t>22,0; 39,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,91; 18,75</t>
+          <t>8,43; 18,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,47; 24,58</t>
+          <t>9,5; 23,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 37,9</t>
+          <t>4,26; 35,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,19</t>
+          <t>0,0; 37,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,25; 36,11</t>
+          <t>21,2; 36,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 14,84</t>
+          <t>6,75; 15,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,34; 22,86</t>
+          <t>9,21; 22,8</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,26; 22,42</t>
+          <t>13,36; 22,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 15,21</t>
+          <t>7,84; 15,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,29; 24,91</t>
+          <t>13,86; 24,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,33; 27,53</t>
+          <t>9,26; 27,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,3</t>
+          <t>3,28; 15,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,79</t>
+          <t>1,16; 11,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,69; 21,73</t>
+          <t>13,53; 21,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,7</t>
+          <t>7,46; 13,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 19,28</t>
+          <t>11,19; 19,49</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 18,02</t>
+          <t>4,05; 18,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,66; 16,58</t>
+          <t>5,66; 16,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,68; 28,93</t>
+          <t>14,16; 28,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 36,79</t>
+          <t>8,88; 36,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 10,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 36,24</t>
+          <t>14,91; 36,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,08; 20,37</t>
+          <t>7,21; 20,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 12,26</t>
+          <t>4,63; 12,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,63; 28,33</t>
+          <t>16,21; 28,86</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1238,37 +1238,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,17</t>
+          <t>0,0; 81,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 18,3</t>
+          <t>1,98; 18,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 30,09</t>
+          <t>7,96; 27,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,38; 34,61</t>
+          <t>6,33; 32,06</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 16,57</t>
+          <t>1,83; 17,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 26,15</t>
+          <t>7,16; 26,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,71; 31,33</t>
+          <t>7,6; 30,81</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,77; 22,01</t>
+          <t>15,97; 22,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,56; 12,78</t>
+          <t>8,59; 12,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12,97; 19,11</t>
+          <t>12,8; 19,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,94</t>
+          <t>10,68; 19,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 12,75</t>
+          <t>6,08; 12,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,32; 17,96</t>
+          <t>10,28; 17,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,34; 20,29</t>
+          <t>15,16; 20,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,98</t>
+          <t>8,45; 12,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12,91; 17,51</t>
+          <t>12,8; 17,38</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9386; 23799</t>
+          <t>9479; 24319</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5484; 22073</t>
+          <t>5519; 21962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3432; 14760</t>
+          <t>3114; 14384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5859</t>
+          <t>0; 6328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3818; 14856</t>
+          <t>3998; 14424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4650; 16014</t>
+          <t>4047; 16547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10729; 26842</t>
+          <t>10420; 25575</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11587; 30217</t>
+          <t>11770; 30620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9960; 26665</t>
+          <t>10032; 25490</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9142; 22969</t>
+          <t>9832; 23734</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2273; 15056</t>
+          <t>2340; 14182</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1982; 11430</t>
+          <t>2074; 11122</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4057; 13555</t>
+          <t>3874; 14029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1908; 11142</t>
+          <t>1985; 11311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3903; 15594</t>
+          <t>3589; 15698</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16084; 32946</t>
+          <t>16488; 33577</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6123; 21165</t>
+          <t>6141; 21629</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7619; 21993</t>
+          <t>7826; 22108</t>
         </is>
       </c>
     </row>
@@ -1965,22 +1965,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>23245; 42834</t>
+          <t>23476; 42634</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12818; 30370</t>
+          <t>13653; 29528</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9311; 24159</t>
+          <t>9341; 23471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1131; 9238</t>
+          <t>1038; 8696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4509</t>
+          <t>0; 4938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26548; 47331</t>
+          <t>27784; 48123</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12868; 29262</t>
+          <t>13305; 30530</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10409; 25478</t>
+          <t>10268; 25421</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36072; 61020</t>
+          <t>36347; 61253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25650; 48506</t>
+          <t>25011; 48692</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32543; 56731</t>
+          <t>31563; 56406</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5907; 17438</t>
+          <t>5864; 17511</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3901; 17316</t>
+          <t>3707; 17324</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1051; 9348</t>
+          <t>1004; 9583</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45909; 72881</t>
+          <t>45376; 73064</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31690; 59194</t>
+          <t>32243; 58245</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>34619; 60627</t>
+          <t>35179; 61277</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2512; 11460</t>
+          <t>2577; 11579</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7192; 21079</t>
+          <t>7190; 20542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14730; 31154</t>
+          <t>15252; 31075</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3078; 13061</t>
+          <t>3153; 12831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 6968</t>
+          <t>0; 7268</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10923; 25441</t>
+          <t>10464; 25853</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7014; 20187</t>
+          <t>7142; 20457</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8797; 24097</t>
+          <t>9109; 23865</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29581; 50401</t>
+          <t>28831; 51343</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2464,37 +2464,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 4518</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>969; 8965</t>
+          <t>968; 9013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4922; 18337</t>
+          <t>4851; 16778</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2304; 12505</t>
+          <t>2289; 11587</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>977; 9031</t>
+          <t>999; 9735</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4999; 17510</t>
+          <t>4796; 17516</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3215; 13067</t>
+          <t>3169; 12849</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98376; 137248</t>
+          <t>99626; 137855</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69852; 104258</t>
+          <t>70060; 105400</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>78537; 115709</t>
+          <t>77530; 115363</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25904; 47492</t>
+          <t>26767; 48486</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>23570; 49017</t>
+          <t>23391; 49378</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34525; 60067</t>
+          <t>34379; 59213</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>134096; 177437</t>
+          <t>132557; 179287</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>100550; 143881</t>
+          <t>101411; 144756</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>121357; 164615</t>
+          <t>120367; 163413</t>
         </is>
       </c>
     </row>
